--- a/output/pdf_financials_xlsx/LINE.xlsx
+++ b/output/pdf_financials_xlsx/LINE.xlsx
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.305577</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.539752</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.723589</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.854903</v>
       </c>
     </row>
     <row r="93">
@@ -4195,7 +4195,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4230,7 +4234,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LINE.xlsx
+++ b/output/pdf_financials_xlsx/LINE.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000156</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000168</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001819</v>
       </c>
     </row>
     <row r="13">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.459661</v>
+        <v>-2.459699</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.691322</v>
+        <v>-4.691478</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.750583</v>
+        <v>-5.750795</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.635073</v>
+        <v>-6.635241</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.313365</v>
+        <v>-3.315184</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.459661</v>
+        <v>-2.459699</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.691322</v>
+        <v>-4.691478</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.750583</v>
+        <v>-5.750795</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.635073</v>
+        <v>-6.635241</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.313365</v>
+        <v>-3.315184</v>
       </c>
     </row>
     <row r="30">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.111486</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.664578</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.704908</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.951807</v>
       </c>
     </row>
     <row r="35">
@@ -1231,16 +1231,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.111486</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.737371</v>
+        <v>4.401949</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.187425</v>
+        <v>1.892333</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.123912</v>
+        <v>1.075719</v>
       </c>
     </row>
     <row r="37">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.887939</v>
+        <v>0.7764529999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.769465</v>
+        <v>1.104887</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.141696</v>
+        <v>0.436788</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.107642</v>
+        <v>0.155835</v>
       </c>
     </row>
     <row r="49">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3811,7 +3811,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -6017,7 +6021,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/LINE.xlsx
+++ b/output/pdf_financials_xlsx/LINE.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.487036</v>
+        <v>0.840787</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.75112</v>
+        <v>1.878953</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.062354</v>
+        <v>1.230121</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.218865</v>
+        <v>1.330365</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.421795</v>
+        <v>0.440695</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.487036</v>
+        <v>0.840787</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.75112</v>
+        <v>1.878953</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.062354</v>
+        <v>1.230121</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.218865</v>
+        <v>1.330365</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.421795</v>
+        <v>0.440695</v>
       </c>
     </row>
     <row r="11">
@@ -1983,16 +1983,16 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.977816</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="68">
@@ -5700,7 +5700,11 @@
           <t>Consultants and directors fees 8 $</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>0.353751</v>
       </c>
